--- a/data/آذین 2/cnc/operations.xlsx
+++ b/data/آذین 2/cnc/operations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayarat-d\Desktop\app\my-crossplatform-app\data\آذین 2\cnc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayarat-d\Desktop\app\my-crossplatform-app\data\cnc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7506830E-BC74-4CA1-99C3-2CFDA4CCAFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4282A2C2-6F6A-446F-88B2-39FBD1E591E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,97 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>پیش مته</t>
+  </si>
+  <si>
+    <t>کانوله-  تک کولت</t>
+  </si>
+  <si>
+    <t>کانوله- دوکولت</t>
+  </si>
+  <si>
+    <t>قلاویز</t>
+  </si>
+  <si>
+    <t>روتراشی</t>
+  </si>
+  <si>
+    <t>مخروطی</t>
+  </si>
+  <si>
+    <t>زاویه سر</t>
+  </si>
+  <si>
+    <t>روتراشی-مخروطی</t>
+  </si>
+  <si>
+    <t>سایزینگ</t>
+  </si>
+  <si>
+    <t>برشکاری</t>
+  </si>
+  <si>
+    <t>سوراخکاری راه به در</t>
+  </si>
+  <si>
+    <t>آج و کات</t>
+  </si>
+  <si>
+    <t>آج زنی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پخ زنی </t>
+  </si>
+  <si>
+    <t>پلیسه گیری هگزا</t>
+  </si>
+  <si>
+    <t>تراشکاری و رزوه زنی</t>
+  </si>
+  <si>
+    <t>پوکه تراشی</t>
+  </si>
+  <si>
+    <t>ماشینکاری</t>
+  </si>
+  <si>
+    <t>سوراخکاری جانبی</t>
+  </si>
+  <si>
+    <t>شیار سطح نیل</t>
+  </si>
+  <si>
+    <t>سوراخکاری تحت زاویه</t>
+  </si>
+  <si>
+    <t>سوراخ بعد از خم</t>
+  </si>
+  <si>
+    <t>شیار بغل</t>
+  </si>
+  <si>
+    <t>فرزکاری</t>
+  </si>
+  <si>
+    <t>ناچ/ شیار</t>
+  </si>
+  <si>
+    <t>باربرداری</t>
+  </si>
+  <si>
+    <t>دورتراشی قطعه</t>
+  </si>
+  <si>
+    <t>زاویه هد</t>
+  </si>
+  <si>
+    <t>سوراخکاری</t>
+  </si>
+  <si>
+    <t>سوراخکاری هد</t>
+  </si>
   <si>
     <t>سوراخکاری ساق</t>
   </si>
@@ -375,173 +465,173 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2</v>
-      </c>
-    </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>222</v>
+      <c r="A24" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2</v>
+      <c r="A25" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>2</v>
+      <c r="A26" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2</v>
+      <c r="A27" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2</v>
+      <c r="A28" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>22</v>
+      <c r="A29" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2</v>
+      <c r="A30" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
